--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/WISCONSIN_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/WISCONSIN_2020.xlsx
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C86">
@@ -3253,7 +3253,7 @@
         <v>8</v>
       </c>
       <c r="D161">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="162">
@@ -4243,7 +4243,7 @@
         <v>8</v>
       </c>
       <c r="D216">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="217">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C218">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C224">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C233">
@@ -4783,7 +4783,7 @@
         <v>8</v>
       </c>
       <c r="D246">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="247">
@@ -4819,7 +4819,7 @@
         <v>8</v>
       </c>
       <c r="D248">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="249">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C308">
@@ -6007,7 +6007,7 @@
         <v>8</v>
       </c>
       <c r="D314">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="315">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C344">
@@ -6889,7 +6889,7 @@
         <v>8</v>
       </c>
       <c r="D363">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="364">
@@ -7447,7 +7447,7 @@
         <v>8</v>
       </c>
       <c r="D394">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="395">
@@ -7897,7 +7897,7 @@
         <v>8</v>
       </c>
       <c r="D419">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="420">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C426">
@@ -8131,7 +8131,7 @@
         <v>8</v>
       </c>
       <c r="D432">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="433">
@@ -8725,7 +8725,7 @@
         <v>8</v>
       </c>
       <c r="D465">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="466">
@@ -9085,7 +9085,7 @@
         <v>8</v>
       </c>
       <c r="D485">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="486">
@@ -9265,7 +9265,7 @@
         <v>8</v>
       </c>
       <c r="D495">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="496">
@@ -10183,7 +10183,7 @@
         <v>8</v>
       </c>
       <c r="D546">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="547">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Cuilapam De Guerero</t>
+          <t>Cuilapam De Guerrero</t>
         </is>
       </c>
       <c r="C570">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C585">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C624">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C652">
@@ -12739,7 +12739,7 @@
         <v>8</v>
       </c>
       <c r="D688">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="689">
@@ -13567,7 +13567,7 @@
         <v>8</v>
       </c>
       <c r="D734">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="735">
@@ -14107,7 +14107,7 @@
         <v>8</v>
       </c>
       <c r="D764">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="765">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C769">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C820">
@@ -15583,7 +15583,7 @@
         <v>8</v>
       </c>
       <c r="D846">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="847">
@@ -16951,7 +16951,7 @@
         <v>8</v>
       </c>
       <c r="D922">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="923">
@@ -18535,7 +18535,7 @@
         <v>8</v>
       </c>
       <c r="D1010">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="1011">
@@ -19363,7 +19363,7 @@
         <v>8</v>
       </c>
       <c r="D1056">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="1057">
@@ -19651,7 +19651,7 @@
         <v>8</v>
       </c>
       <c r="D1072">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="1073">
@@ -20191,7 +20191,7 @@
         <v>8</v>
       </c>
       <c r="D1102">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="1103">
@@ -20389,7 +20389,7 @@
         <v>8</v>
       </c>
       <c r="D1113">
-        <v>0.0009381963175794535</v>
+        <v>0.0009381963175794536</v>
       </c>
     </row>
     <row r="1114">
